--- a/files/Boards Results.xlsx
+++ b/files/Boards Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T153"/>
+  <dimension ref="A1:W153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,15 +516,30 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Sub6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Marks6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Grade6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -606,13 +621,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
         <v>428</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -694,13 +712,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>326</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>65.2</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -782,13 +803,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>417</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -870,13 +894,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>401</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>80.2</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -958,13 +985,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
         <v>349</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>69.8</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1046,13 +1076,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>424</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>84.8</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1134,13 +1167,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>441</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>88.2</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1222,13 +1258,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
         <v>483</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1310,13 +1349,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
         <v>424</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>84.8</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1398,13 +1440,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>401</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>80.2</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1486,13 +1531,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>324</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>64.8</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1574,13 +1622,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>350</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>70</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1662,13 +1713,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
         <v>316</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>63.2</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1750,13 +1804,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
         <v>350</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>70</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1838,13 +1895,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
         <v>368</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1926,13 +1986,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
         <v>338</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2014,13 +2077,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
         <v>423</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2102,13 +2168,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
         <v>395</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>79</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2190,13 +2259,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
         <v>393</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2278,13 +2350,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
         <v>375</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>75</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2366,13 +2441,16 @@
           <t>D2</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
         <v>276</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>55.2</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>COMP</t>
         </is>
@@ -2454,13 +2532,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
         <v>412</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2542,13 +2623,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
         <v>336</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>67.2</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2630,13 +2714,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
         <v>392</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2718,13 +2805,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
         <v>386</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>77.2</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2806,13 +2896,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
         <v>427</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2894,13 +2987,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
         <v>340</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>68</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2982,13 +3078,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
         <v>388</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3070,13 +3169,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
         <v>338</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3158,13 +3260,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
         <v>424</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>84.8</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3246,13 +3351,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
         <v>452</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3334,13 +3442,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
         <v>370</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>74</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3422,13 +3533,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
         <v>394</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>78.8</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3510,13 +3624,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
         <v>316</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>63.2</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>COMP</t>
         </is>
@@ -3598,13 +3715,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
         <v>394</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>78.8</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3686,13 +3806,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="n">
         <v>451</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>90.2</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3774,13 +3897,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
         <v>417</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3862,13 +3988,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="n">
         <v>394</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>78.8</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3950,13 +4079,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="n">
         <v>410</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>82</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4038,13 +4170,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
         <v>421</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>84.2</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4126,13 +4261,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
         <v>353</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4214,13 +4352,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
         <v>428</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4302,13 +4443,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
         <v>324</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>64.8</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4390,13 +4534,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
         <v>337</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4478,13 +4625,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
         <v>302</v>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
         <v>60.4</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4566,13 +4716,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
         <v>343</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4654,13 +4807,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
         <v>396</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>79.2</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4742,13 +4898,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
         <v>330</v>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
         <v>66</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4830,13 +4989,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
         <v>374</v>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
         <v>74.8</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4918,13 +5080,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
         <v>417</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5006,13 +5171,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="n">
         <v>469</v>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
         <v>93.8</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5094,13 +5262,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="n">
         <v>259</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>51.8</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>COMP</t>
         </is>
@@ -5182,13 +5353,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R54" t="n">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="n">
         <v>353</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5270,13 +5444,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="n">
         <v>389</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>77.8</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5358,13 +5535,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R56" t="n">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="n">
         <v>419</v>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
         <v>83.8</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5446,13 +5626,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R57" t="n">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="n">
         <v>435</v>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
         <v>87</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5534,13 +5717,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R58" t="n">
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="n">
         <v>401</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>80.2</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5622,13 +5808,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R59" t="n">
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="n">
         <v>437</v>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5710,13 +5899,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R60" t="n">
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="n">
         <v>460</v>
       </c>
-      <c r="S60" t="n">
+      <c r="V60" t="n">
         <v>92</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5798,13 +5990,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
         <v>377</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5886,13 +6081,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R62" t="n">
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="n">
         <v>392</v>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5974,13 +6172,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R63" t="n">
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
         <v>368</v>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6062,13 +6263,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R64" t="n">
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="n">
         <v>413</v>
       </c>
-      <c r="S64" t="n">
+      <c r="V64" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6150,13 +6354,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R65" t="n">
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
         <v>318</v>
       </c>
-      <c r="S65" t="n">
+      <c r="V65" t="n">
         <v>63.6</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6238,13 +6445,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R66" t="n">
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="n">
         <v>447</v>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6326,13 +6536,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R67" t="n">
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="n">
         <v>445</v>
       </c>
-      <c r="S67" t="n">
+      <c r="V67" t="n">
         <v>89</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6414,13 +6627,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="n">
         <v>404</v>
       </c>
-      <c r="S68" t="n">
+      <c r="V68" t="n">
         <v>80.8</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6502,13 +6718,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R69" t="n">
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="n">
         <v>430</v>
       </c>
-      <c r="S69" t="n">
+      <c r="V69" t="n">
         <v>86</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6590,13 +6809,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R70" t="n">
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="n">
         <v>425</v>
       </c>
-      <c r="S70" t="n">
+      <c r="V70" t="n">
         <v>85</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6678,13 +6900,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R71" t="n">
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="n">
         <v>341</v>
       </c>
-      <c r="S71" t="n">
+      <c r="V71" t="n">
         <v>68.2</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6766,13 +6991,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R72" t="n">
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="n">
         <v>407</v>
       </c>
-      <c r="S72" t="n">
+      <c r="V72" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6854,13 +7082,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R73" t="n">
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="n">
         <v>475</v>
       </c>
-      <c r="S73" t="n">
+      <c r="V73" t="n">
         <v>95</v>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6942,13 +7173,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R74" t="n">
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="n">
         <v>417</v>
       </c>
-      <c r="S74" t="n">
+      <c r="V74" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7030,13 +7264,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R75" t="n">
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="n">
         <v>411</v>
       </c>
-      <c r="S75" t="n">
+      <c r="V75" t="n">
         <v>82.2</v>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7118,13 +7355,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R76" t="n">
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="n">
         <v>352</v>
       </c>
-      <c r="S76" t="n">
+      <c r="V76" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7206,13 +7446,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R77" t="n">
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="n">
         <v>326</v>
       </c>
-      <c r="S77" t="n">
+      <c r="V77" t="n">
         <v>65.2</v>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7294,13 +7537,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R78" t="n">
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="n">
         <v>299</v>
       </c>
-      <c r="S78" t="n">
+      <c r="V78" t="n">
         <v>59.8</v>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7382,13 +7628,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R79" t="n">
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="n">
         <v>320</v>
       </c>
-      <c r="S79" t="n">
+      <c r="V79" t="n">
         <v>64</v>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7470,13 +7719,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R80" t="n">
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="n">
         <v>427</v>
       </c>
-      <c r="S80" t="n">
+      <c r="V80" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7558,13 +7810,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R81" t="n">
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="n">
         <v>415</v>
       </c>
-      <c r="S81" t="n">
+      <c r="V81" t="n">
         <v>83</v>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7646,13 +7901,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R82" t="n">
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="n">
         <v>360</v>
       </c>
-      <c r="S82" t="n">
+      <c r="V82" t="n">
         <v>72</v>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7734,13 +7992,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R83" t="n">
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="n">
         <v>394</v>
       </c>
-      <c r="S83" t="n">
+      <c r="V83" t="n">
         <v>78.8</v>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7822,13 +8083,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R84" t="n">
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="n">
         <v>363</v>
       </c>
-      <c r="S84" t="n">
+      <c r="V84" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7910,13 +8174,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R85" t="n">
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="n">
         <v>310</v>
       </c>
-      <c r="S85" t="n">
+      <c r="V85" t="n">
         <v>62</v>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7998,13 +8265,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R86" t="n">
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="n">
         <v>369</v>
       </c>
-      <c r="S86" t="n">
+      <c r="V86" t="n">
         <v>73.8</v>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8086,13 +8356,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R87" t="n">
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="n">
         <v>353</v>
       </c>
-      <c r="S87" t="n">
+      <c r="V87" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="W87" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8174,13 +8447,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R88" t="n">
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="n">
         <v>400</v>
       </c>
-      <c r="S88" t="n">
+      <c r="V88" t="n">
         <v>80</v>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8262,13 +8538,16 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="R89" t="n">
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="n">
         <v>289</v>
       </c>
-      <c r="S89" t="n">
+      <c r="V89" t="n">
         <v>57.8</v>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8300,13 +8579,16 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="n">
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="n">
+      <c r="V90" t="n">
         <v>0</v>
       </c>
-      <c r="T90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8384,13 +8666,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R91" t="n">
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="n">
         <v>454</v>
       </c>
-      <c r="S91" t="n">
+      <c r="V91" t="n">
         <v>90.8</v>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="W91" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8472,13 +8757,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R92" t="n">
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="n">
         <v>448</v>
       </c>
-      <c r="S92" t="n">
+      <c r="V92" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="W92" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8560,13 +8848,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R93" t="n">
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="n">
         <v>417</v>
       </c>
-      <c r="S93" t="n">
+      <c r="V93" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="W93" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8648,13 +8939,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R94" t="n">
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="n">
         <v>379</v>
       </c>
-      <c r="S94" t="n">
+      <c r="V94" t="n">
         <v>75.8</v>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="W94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8736,13 +9030,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R95" t="n">
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="n">
         <v>333</v>
       </c>
-      <c r="S95" t="n">
+      <c r="V95" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="W95" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8824,13 +9121,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R96" t="n">
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="n">
         <v>420</v>
       </c>
-      <c r="S96" t="n">
+      <c r="V96" t="n">
         <v>84</v>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="W96" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8912,13 +9212,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R97" t="n">
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="n">
         <v>475</v>
       </c>
-      <c r="S97" t="n">
+      <c r="V97" t="n">
         <v>95</v>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9000,13 +9303,16 @@
           <t>D2</t>
         </is>
       </c>
-      <c r="R98" t="n">
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="n">
         <v>290</v>
       </c>
-      <c r="S98" t="n">
+      <c r="V98" t="n">
         <v>58</v>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="W98" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9088,13 +9394,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R99" t="n">
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="n">
         <v>419</v>
       </c>
-      <c r="S99" t="n">
+      <c r="V99" t="n">
         <v>83.8</v>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9176,13 +9485,16 @@
           <t>D2</t>
         </is>
       </c>
-      <c r="R100" t="n">
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="n">
         <v>265</v>
       </c>
-      <c r="S100" t="n">
+      <c r="V100" t="n">
         <v>53</v>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="W100" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9264,13 +9576,16 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="R101" t="n">
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="n">
         <v>309</v>
       </c>
-      <c r="S101" t="n">
+      <c r="V101" t="n">
         <v>61.8</v>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="W101" t="inlineStr">
         <is>
           <t>COMP</t>
         </is>
@@ -9352,13 +9667,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R102" t="n">
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="n">
         <v>407</v>
       </c>
-      <c r="S102" t="n">
+      <c r="V102" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="W102" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9440,13 +9758,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R103" t="n">
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="n">
         <v>349</v>
       </c>
-      <c r="S103" t="n">
+      <c r="V103" t="n">
         <v>69.8</v>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="W103" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9528,13 +9849,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R104" t="n">
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="n">
         <v>364</v>
       </c>
-      <c r="S104" t="n">
+      <c r="V104" t="n">
         <v>72.8</v>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="W104" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9616,13 +9940,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R105" t="n">
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="n">
         <v>457</v>
       </c>
-      <c r="S105" t="n">
+      <c r="V105" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="W105" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9704,13 +10031,16 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="R106" t="n">
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="n">
         <v>306</v>
       </c>
-      <c r="S106" t="n">
+      <c r="V106" t="n">
         <v>61.2</v>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="W106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9792,13 +10122,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R107" t="n">
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="n">
         <v>364</v>
       </c>
-      <c r="S107" t="n">
+      <c r="V107" t="n">
         <v>72.8</v>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="W107" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9880,13 +10213,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R108" t="n">
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="n">
         <v>371</v>
       </c>
-      <c r="S108" t="n">
+      <c r="V108" t="n">
         <v>74.2</v>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="W108" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -9968,13 +10304,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R109" t="n">
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="n">
         <v>474</v>
       </c>
-      <c r="S109" t="n">
+      <c r="V109" t="n">
         <v>94.8</v>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="W109" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10056,13 +10395,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R110" t="n">
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="n">
         <v>479</v>
       </c>
-      <c r="S110" t="n">
+      <c r="V110" t="n">
         <v>95.8</v>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="W110" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10144,13 +10486,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R111" t="n">
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="n">
         <v>468</v>
       </c>
-      <c r="S111" t="n">
+      <c r="V111" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="W111" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10232,13 +10577,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R112" t="n">
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="n">
         <v>474</v>
       </c>
-      <c r="S112" t="n">
+      <c r="V112" t="n">
         <v>94.8</v>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="W112" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10320,13 +10668,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R113" t="n">
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="n">
         <v>460</v>
       </c>
-      <c r="S113" t="n">
+      <c r="V113" t="n">
         <v>92</v>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="W113" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10408,13 +10759,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R114" t="n">
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="n">
         <v>474</v>
       </c>
-      <c r="S114" t="n">
+      <c r="V114" t="n">
         <v>94.8</v>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="W114" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10496,13 +10850,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R115" t="n">
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="n">
         <v>484</v>
       </c>
-      <c r="S115" t="n">
+      <c r="V115" t="n">
         <v>96.8</v>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="W115" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10584,13 +10941,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R116" t="n">
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="n">
         <v>404</v>
       </c>
-      <c r="S116" t="n">
+      <c r="V116" t="n">
         <v>80.8</v>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="W116" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10672,13 +11032,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R117" t="n">
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="n">
         <v>393</v>
       </c>
-      <c r="S117" t="n">
+      <c r="V117" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="W117" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10760,13 +11123,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R118" t="n">
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="n">
         <v>411</v>
       </c>
-      <c r="S118" t="n">
+      <c r="V118" t="n">
         <v>82.2</v>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="W118" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10848,13 +11214,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R119" t="n">
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="n">
         <v>398</v>
       </c>
-      <c r="S119" t="n">
+      <c r="V119" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="W119" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -10936,13 +11305,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R120" t="n">
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="n">
         <v>413</v>
       </c>
-      <c r="S120" t="n">
+      <c r="V120" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="W120" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11024,13 +11396,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R121" t="n">
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="n">
         <v>466</v>
       </c>
-      <c r="S121" t="n">
+      <c r="V121" t="n">
         <v>93.2</v>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="W121" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11112,13 +11487,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R122" t="n">
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="n">
         <v>433</v>
       </c>
-      <c r="S122" t="n">
+      <c r="V122" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="W122" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11200,13 +11578,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R123" t="n">
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="n">
         <v>404</v>
       </c>
-      <c r="S123" t="n">
+      <c r="V123" t="n">
         <v>80.8</v>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="W123" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11288,13 +11669,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R124" t="n">
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="n">
         <v>476</v>
       </c>
-      <c r="S124" t="n">
+      <c r="V124" t="n">
         <v>95.2</v>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="W124" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11376,13 +11760,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R125" t="n">
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="n">
         <v>434</v>
       </c>
-      <c r="S125" t="n">
+      <c r="V125" t="n">
         <v>86.8</v>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="W125" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11464,13 +11851,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R126" t="n">
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="n">
         <v>384</v>
       </c>
-      <c r="S126" t="n">
+      <c r="V126" t="n">
         <v>76.8</v>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="W126" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11552,13 +11942,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="R127" t="n">
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="n">
         <v>331</v>
       </c>
-      <c r="S127" t="n">
+      <c r="V127" t="n">
         <v>66.2</v>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="W127" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11640,13 +12033,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R128" t="n">
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="n">
         <v>466</v>
       </c>
-      <c r="S128" t="n">
+      <c r="V128" t="n">
         <v>93.2</v>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="W128" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11728,13 +12124,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R129" t="n">
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="n">
         <v>465</v>
       </c>
-      <c r="S129" t="n">
+      <c r="V129" t="n">
         <v>93</v>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="W129" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11816,13 +12215,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R130" t="n">
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="n">
         <v>475</v>
       </c>
-      <c r="S130" t="n">
+      <c r="V130" t="n">
         <v>95</v>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="W130" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11904,13 +12306,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R131" t="n">
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="n">
         <v>470</v>
       </c>
-      <c r="S131" t="n">
+      <c r="V131" t="n">
         <v>94</v>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="W131" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -11992,13 +12397,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R132" t="n">
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="n">
         <v>464</v>
       </c>
-      <c r="S132" t="n">
+      <c r="V132" t="n">
         <v>92.8</v>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="W132" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12080,13 +12488,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R133" t="n">
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="n">
         <v>421</v>
       </c>
-      <c r="S133" t="n">
+      <c r="V133" t="n">
         <v>84.2</v>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="W133" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12168,13 +12579,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R134" t="n">
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="n">
         <v>472</v>
       </c>
-      <c r="S134" t="n">
+      <c r="V134" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="W134" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12256,13 +12670,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R135" t="n">
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="n">
         <v>459</v>
       </c>
-      <c r="S135" t="n">
+      <c r="V135" t="n">
         <v>91.8</v>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="W135" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12344,13 +12761,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R136" t="n">
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="n">
         <v>381</v>
       </c>
-      <c r="S136" t="n">
+      <c r="V136" t="n">
         <v>76.2</v>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="W136" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12432,13 +12852,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R137" t="n">
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="n">
         <v>407</v>
       </c>
-      <c r="S137" t="n">
+      <c r="V137" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="W137" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12520,13 +12943,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R138" t="n">
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="n">
         <v>455</v>
       </c>
-      <c r="S138" t="n">
+      <c r="V138" t="n">
         <v>91</v>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="W138" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12608,13 +13034,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R139" t="n">
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="n">
         <v>452</v>
       </c>
-      <c r="S139" t="n">
+      <c r="V139" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="W139" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12696,13 +13125,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R140" t="n">
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="n">
         <v>477</v>
       </c>
-      <c r="S140" t="n">
+      <c r="V140" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="W140" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12784,13 +13216,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R141" t="n">
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="n">
         <v>464</v>
       </c>
-      <c r="S141" t="n">
+      <c r="V141" t="n">
         <v>92.8</v>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="W141" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12872,13 +13307,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R142" t="n">
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="n">
         <v>450</v>
       </c>
-      <c r="S142" t="n">
+      <c r="V142" t="n">
         <v>90</v>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="W142" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -12960,13 +13398,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R143" t="n">
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="n">
         <v>455</v>
       </c>
-      <c r="S143" t="n">
+      <c r="V143" t="n">
         <v>91</v>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="W143" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13048,13 +13489,16 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="R144" t="n">
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="n">
         <v>464</v>
       </c>
-      <c r="S144" t="n">
+      <c r="V144" t="n">
         <v>92.8</v>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="W144" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13136,13 +13580,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R145" t="n">
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="n">
         <v>434</v>
       </c>
-      <c r="S145" t="n">
+      <c r="V145" t="n">
         <v>86.8</v>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="W145" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13224,13 +13671,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R146" t="n">
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="n">
         <v>406</v>
       </c>
-      <c r="S146" t="n">
+      <c r="V146" t="n">
         <v>81.2</v>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="W146" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13312,13 +13762,16 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="R147" t="n">
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="n">
         <v>459</v>
       </c>
-      <c r="S147" t="n">
+      <c r="V147" t="n">
         <v>91.8</v>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="W147" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13400,13 +13853,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="R148" t="n">
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="n">
         <v>332</v>
       </c>
-      <c r="S148" t="n">
+      <c r="V148" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="W148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13488,13 +13944,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R149" t="n">
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="n">
         <v>421</v>
       </c>
-      <c r="S149" t="n">
+      <c r="V149" t="n">
         <v>84.2</v>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="W149" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13576,13 +14035,16 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="R150" t="n">
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="n">
         <v>438</v>
       </c>
-      <c r="S150" t="n">
+      <c r="V150" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="W150" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13664,13 +14126,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R151" t="n">
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="n">
         <v>427</v>
       </c>
-      <c r="S151" t="n">
+      <c r="V151" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="W151" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13752,13 +14217,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R152" t="n">
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="n">
         <v>400</v>
       </c>
-      <c r="S152" t="n">
+      <c r="V152" t="n">
         <v>80</v>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="W152" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -13840,13 +14308,16 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="R153" t="n">
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="n">
         <v>449</v>
       </c>
-      <c r="S153" t="n">
+      <c r="V153" t="n">
         <v>89.8</v>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="W153" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
